--- a/apps/landing/public/samples/EcoMiles_Mau_FMCG_80_Don_TPHCM.xlsx
+++ b/apps/landing/public/samples/EcoMiles_Mau_FMCG_80_Don_TPHCM.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="orders" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Doi_Xe_Hien_Co" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,18 +495,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23 Nguyễn Thị Thập, P. Tân Phú, Quận 7, TP.HCM</t>
+          <t>23 Tô Hiến Thành, Phường 15, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.741608</v>
+        <v>10.781563</v>
       </c>
       <c r="D2" t="n">
-        <v>106.712684</v>
+        <v>106.661973</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GS25 - CN Quận 7 #01</t>
+          <t>GS25 - CN Quận 10 #01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -533,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -545,18 +546,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>36 Nguyễn Văn Trỗi, Phường 8, Phú Nhuận, TP.HCM</t>
+          <t>36 Lạc Long Quân, Phường 10, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.795384</v>
+        <v>10.780333</v>
       </c>
       <c r="D3" t="n">
-        <v>106.671288</v>
+        <v>106.644755</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Phú Nhuận #02</t>
+          <t>Nhà hàng Golden Gate - CN Tân Bình #02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -584,7 +585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -596,18 +597,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>49 Lê Lợi, P. Bến Thành, Quận 1, TP.HCM</t>
+          <t>49 Nguyễn Hữu Cảnh, Phường 22, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.77169</v>
+        <v>10.792636</v>
       </c>
       <c r="D4" t="n">
-        <v>106.696632</v>
+        <v>106.718133</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Quận 1 #03</t>
+          <t>Đại lý Phân Phối Minh Phát - CN Bình Thạnh #03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -635,7 +636,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -647,18 +648,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>62 Nguyễn Văn Linh, P. Tân Phong, Quận 7, TP.HCM</t>
+          <t>62 Đinh Tiên Hoàng, P. Đa Kao, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.726832</v>
+        <v>10.788733</v>
       </c>
       <c r="D5" t="n">
-        <v>106.706616</v>
+        <v>106.696927</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Co.op Food - CN Quận 7 #04</t>
+          <t>Co.op Food - CN Quận 1 #04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -686,7 +687,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -698,18 +699,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>75 Cộng Hòa, Phường 13, Tân Bình, TP.HCM</t>
+          <t>75 Trần Hưng Đạo, Phường 2, Quận 5, TP.HCM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.806442</v>
+        <v>10.757937</v>
       </c>
       <c r="D6" t="n">
-        <v>106.650614</v>
+        <v>106.681866</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Tân Bình #05</t>
+          <t>Siêu thị Ân Nam - CN Quận 5 #05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -737,7 +738,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -749,18 +750,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88 Hai Bà Trưng, P. Tân Định, Quận 1, TP.HCM</t>
+          <t>88 Nguyễn Văn Trỗi, Phường 11, Phú Nhuận, TP.HCM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.791333</v>
+        <v>10.795053</v>
       </c>
       <c r="D7" t="n">
-        <v>106.693051</v>
+        <v>106.67446</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Quận 1 #06</t>
+          <t>Phúc Long Hub - CN Phú Nhuận #06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -788,7 +789,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Phú Nhuận</t>
         </is>
       </c>
     </row>
@@ -800,18 +801,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>101 Sư Vạn Hạnh, Phường 12, Quận 10, TP.HCM</t>
+          <t>101 Trần Não, P. An Khánh, TP. Thủ Đức, TP.HCM</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.773652</v>
+        <v>10.789481</v>
       </c>
       <c r="D8" t="n">
-        <v>106.668547</v>
+        <v>106.731799</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Quận 10 #07</t>
+          <t>WinMart+ - CN TP. Thủ Đức #07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -839,7 +840,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -851,18 +852,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>114 Trường Chinh, Phường 15, Tân Bình, TP.HCM</t>
+          <t>114 Kỳ Đồng, Phường 9, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.818867</v>
+        <v>10.783347</v>
       </c>
       <c r="D9" t="n">
-        <v>106.627598</v>
+        <v>106.679119</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Circle K - CN Tân Bình #08</t>
+          <t>Circle K - CN Quận 3 #08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -890,7 +891,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -902,18 +903,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>127 Võ Văn Tần, Phường 6, Quận 3, TP.HCM</t>
+          <t>127 Cộng Hòa, Phường 13, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.77538</v>
+        <v>10.800792</v>
       </c>
       <c r="D10" t="n">
-        <v>106.687178</v>
+        <v>106.640571</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Quận 3 #09</t>
+          <t>Highlands Coffee - CN Tân Bình #09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -941,7 +942,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -953,18 +954,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140 Ba Tháng Hai, Phường 11, Quận 10, TP.HCM</t>
+          <t>140 Bạch Đằng, Phường 15, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.773135</v>
+        <v>10.803854</v>
       </c>
       <c r="D11" t="n">
-        <v>106.674412</v>
+        <v>106.702285</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 10 #10</t>
+          <t>Bách Hóa Xanh - CN Bình Thạnh #10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -992,7 +993,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1004,18 +1005,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>153 Võ Văn Ngân, P. Linh Chiểu, TP. Thủ Đức, TP.HCM</t>
+          <t>153 Nguyễn Trãi, P. Nguyễn Cư Trinh, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.852345</v>
+        <v>10.766938</v>
       </c>
       <c r="D12" t="n">
-        <v>106.768295</v>
+        <v>106.689138</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GS25 - CN TP. Thủ Đức #11</t>
+          <t>GS25 - CN Quận 1 #11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1043,7 +1044,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1055,18 +1056,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>166 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3, TP.HCM</t>
+          <t>166 Nguyễn Tri Phương, Phường 8, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.790306</v>
+        <v>10.763202</v>
       </c>
       <c r="D13" t="n">
-        <v>106.681855</v>
+        <v>106.666682</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Quận 3 #12</t>
+          <t>Nhà hàng Golden Gate - CN Quận 10 #12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1094,7 +1095,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 10</t>
         </is>
       </c>
     </row>
@@ -1106,18 +1107,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>179 Điện Biên Phủ, Phường 25, Bình Thạnh, TP.HCM</t>
+          <t>179 Hòa Bình, P. Hiệp Tân, Tân Phú, TP.HCM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.797855</v>
+        <v>10.767162</v>
       </c>
       <c r="D14" t="n">
-        <v>106.710648</v>
+        <v>106.631959</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Bình Thạnh #13</t>
+          <t>Đại lý Phân Phối Minh Phát - CN Tân Phú #13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1145,7 +1146,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Phú; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1157,18 +1158,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>192 Xa Lộ Hà Nội, P. An Phú, TP. Thủ Đức, TP.HCM</t>
+          <t>192 Huỳnh Tấn Phát, P. Bình Thuận, Quận 7, TP.HCM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.802</v>
+        <v>10.7424</v>
       </c>
       <c r="D15" t="n">
-        <v>106.74641</v>
+        <v>106.727244</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Co.op Food - CN TP. Thủ Đức #14</t>
+          <t>Co.op Food - CN Quận 7 #14</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1196,7 +1197,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1208,18 +1209,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>205 Trần Hưng Đạo, Phường 7, Quận 5, TP.HCM</t>
+          <t>205 Điện Biên Phủ, Phường 4, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.75659</v>
+        <v>10.775216</v>
       </c>
       <c r="D16" t="n">
-        <v>106.669385</v>
+        <v>106.679954</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Quận 5 #15</t>
+          <t>Siêu thị Ân Nam - CN Quận 3 #15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1247,7 +1248,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1259,18 +1260,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>218 Phan Đăng Lưu, Phường 3, Bình Thạnh, TP.HCM</t>
+          <t>218 Hậu Giang, Phường 6, Quận 6, TP.HCM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.802439</v>
+        <v>10.749076</v>
       </c>
       <c r="D17" t="n">
-        <v>106.689917</v>
+        <v>106.645987</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Bình Thạnh #16</t>
+          <t>Phúc Long Hub - CN Quận 6 #16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1298,7 +1299,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 6; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1310,14 +1311,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>231 Quang Trung, Phường 10, Gò Vấp, TP.HCM</t>
+          <t>231 Nguyễn Oanh, Phường 17, Gò Vấp, TP.HCM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.834325</v>
+        <v>10.83593</v>
       </c>
       <c r="D18" t="n">
-        <v>106.658117</v>
+        <v>106.675087</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1361,18 +1362,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>244 Nguyễn Trãi, Phường 11, Quận 5, TP.HCM</t>
+          <t>244 Hai Bà Trưng, P. Tân Định, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.75183</v>
+        <v>10.789952</v>
       </c>
       <c r="D19" t="n">
-        <v>106.661129</v>
+        <v>106.690292</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Circle K - CN Quận 5 #18</t>
+          <t>Circle K - CN Quận 1 #18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1400,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 1</t>
         </is>
       </c>
     </row>
@@ -1412,18 +1413,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>257 Phan Xích Long, Phường 2, Phú Nhuận, TP.HCM</t>
+          <t>257 Thành Thái, Phường 14, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.801522</v>
+        <v>10.774609</v>
       </c>
       <c r="D20" t="n">
-        <v>106.68557</v>
+        <v>106.661508</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Phú Nhuận #19</t>
+          <t>Highlands Coffee - CN Quận 10 #19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1451,7 +1452,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1463,18 +1464,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>270 Nguyễn Huệ, P. Bến Nghé, Quận 1, TP.HCM</t>
+          <t>270 Bàu Cát, Phường 14, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.771286</v>
+        <v>10.790195</v>
       </c>
       <c r="D21" t="n">
-        <v>106.706679</v>
+        <v>106.642992</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 1 #20</t>
+          <t>Bách Hóa Xanh - CN Tân Bình #20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1502,7 +1503,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1514,18 +1515,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>283 Nguyễn Thị Thập, P. Tân Phú, Quận 7, TP.HCM</t>
+          <t>283 Hoàng Diệu, Phường 6, Quận 4, TP.HCM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10.737465</v>
+        <v>10.760506</v>
       </c>
       <c r="D22" t="n">
-        <v>106.715646</v>
+        <v>106.701158</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GS25 - CN Quận 7 #21</t>
+          <t>GS25 - CN Quận 4 #21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1553,7 +1554,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 4; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1565,18 +1566,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>296 Nguyễn Văn Trỗi, Phường 8, Phú Nhuận, TP.HCM</t>
+          <t>296 Võ Văn Tần, Phường 6, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10.794221</v>
+        <v>10.776169</v>
       </c>
       <c r="D23" t="n">
-        <v>106.673806</v>
+        <v>106.689463</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Phú Nhuận #22</t>
+          <t>Nhà hàng Golden Gate - CN Quận 3 #22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1604,7 +1605,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1616,18 +1617,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>309 Lê Lợi, P. Bến Thành, Quận 1, TP.HCM</t>
+          <t>309 An Dương Vương, Phường 4, Quận 5, TP.HCM</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10.768875</v>
+        <v>10.75891</v>
       </c>
       <c r="D24" t="n">
-        <v>106.698147</v>
+        <v>106.677139</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Quận 1 #23</t>
+          <t>Đại lý Phân Phối Minh Phát - CN Quận 5 #23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1655,7 +1656,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1667,18 +1668,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>322 Nguyễn Văn Linh, P. Tân Phong, Quận 7, TP.HCM</t>
+          <t>322 Huỳnh Văn Bánh, Phường 17, Phú Nhuận, TP.HCM</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10.733593</v>
+        <v>10.793437</v>
       </c>
       <c r="D25" t="n">
-        <v>106.713049</v>
+        <v>106.6805</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Co.op Food - CN Quận 7 #24</t>
+          <t>Co.op Food - CN Phú Nhuận #24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1706,7 +1707,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Phú Nhuận</t>
         </is>
       </c>
     </row>
@@ -1718,18 +1719,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>335 Cộng Hòa, Phường 13, Tân Bình, TP.HCM</t>
+          <t>335 Phạm Văn Đồng, P. Hiệp Bình Chánh, TP. Thủ Đức, TP.HCM</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.803741</v>
+        <v>10.828156</v>
       </c>
       <c r="D26" t="n">
-        <v>106.649215</v>
+        <v>106.722606</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Tân Bình #25</t>
+          <t>Siêu thị Ân Nam - CN TP. Thủ Đức #25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1757,7 +1758,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1769,18 +1770,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>348 Hai Bà Trưng, P. Tân Định, Quận 1, TP.HCM</t>
+          <t>348 Ba Tháng Hai, Phường 12, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10.793497</v>
+        <v>10.773219</v>
       </c>
       <c r="D27" t="n">
-        <v>106.693018</v>
+        <v>106.670447</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Quận 1 #26</t>
+          <t>Phúc Long Hub - CN Quận 10 #26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1808,7 +1809,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1820,18 +1821,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>361 Sư Vạn Hạnh, Phường 12, Quận 10, TP.HCM</t>
+          <t>361 Hoàng Văn Thụ, Phường 4, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10.772922</v>
+        <v>10.798189</v>
       </c>
       <c r="D28" t="n">
-        <v>106.664804</v>
+        <v>106.655602</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Quận 10 #27</t>
+          <t>WinMart+ - CN Tân Bình #27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1859,7 +1860,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1871,18 +1872,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>374 Trường Chinh, Phường 15, Tân Bình, TP.HCM</t>
+          <t>374 Nguyễn Gia Trí (D2), Phường 25, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.817375</v>
+        <v>10.80405</v>
       </c>
       <c r="D29" t="n">
-        <v>106.62843</v>
+        <v>106.714852</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Circle K - CN Tân Bình #28</t>
+          <t>Circle K - CN Bình Thạnh #28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1910,7 +1911,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1922,18 +1923,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>387 Võ Văn Tần, Phường 6, Quận 3, TP.HCM</t>
+          <t>387 Trần Hưng Đạo, P. Cầu Kho, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.780472</v>
+        <v>10.763129</v>
       </c>
       <c r="D30" t="n">
-        <v>106.691042</v>
+        <v>106.689417</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Quận 3 #29</t>
+          <t>Highlands Coffee - CN Quận 1 #29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1961,7 +1962,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -1973,18 +1974,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20 Ba Tháng Hai, Phường 11, Quận 10, TP.HCM</t>
+          <t>20 Ông Ích Khiêm, Phường 10, Quận 11, TP.HCM</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.774476</v>
+        <v>10.76739</v>
       </c>
       <c r="D31" t="n">
-        <v>106.674513</v>
+        <v>106.644025</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 10 #30</t>
+          <t>Bách Hóa Xanh - CN Quận 11 #30</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2012,7 +2013,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 11</t>
         </is>
       </c>
     </row>
@@ -2024,18 +2025,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>33 Võ Văn Ngân, P. Linh Chiểu, TP. Thủ Đức, TP.HCM</t>
+          <t>33 Phan Xích Long, Phường 2, Phú Nhuận, TP.HCM</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.846102</v>
+        <v>10.796441</v>
       </c>
       <c r="D32" t="n">
-        <v>106.760178</v>
+        <v>106.687891</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GS25 - CN TP. Thủ Đức #31</t>
+          <t>GS25 - CN Phú Nhuận #31</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2063,7 +2064,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2075,18 +2076,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>46 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3, TP.HCM</t>
+          <t>46 Dương Bá Trạc, Phường 1, Quận 8, TP.HCM</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10.790667</v>
+        <v>10.748047</v>
       </c>
       <c r="D33" t="n">
-        <v>106.679746</v>
+        <v>106.686138</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Quận 3 #32</t>
+          <t>Nhà hàng Golden Gate - CN Quận 8 #32</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2114,7 +2115,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 8; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2126,18 +2127,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>59 Điện Biên Phủ, Phường 25, Bình Thạnh, TP.HCM</t>
+          <t>59 Lê Văn Sỹ, Phường 14, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10.804045</v>
+        <v>10.790338</v>
       </c>
       <c r="D34" t="n">
-        <v>106.71851</v>
+        <v>106.679804</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Bình Thạnh #33</t>
+          <t>Đại lý Phân Phối Minh Phát - CN Quận 3 #33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2165,7 +2166,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2177,18 +2178,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>72 Xa Lộ Hà Nội, P. An Phú, TP. Thủ Đức, TP.HCM</t>
+          <t>72 Kinh Dương Vương, Phường 12, Quận 6, TP.HCM</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10.799239</v>
+        <v>10.750695</v>
       </c>
       <c r="D35" t="n">
-        <v>106.740273</v>
+        <v>106.633389</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Co.op Food - CN TP. Thủ Đức #34</t>
+          <t>Co.op Food - CN Quận 6 #34</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2216,7 +2217,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 6; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2228,18 +2229,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>85 Trần Hưng Đạo, Phường 7, Quận 5, TP.HCM</t>
+          <t>85 Xô Viết Nghệ Tĩnh, Phường 21, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10.750567</v>
+        <v>10.795807</v>
       </c>
       <c r="D36" t="n">
-        <v>106.672859</v>
+        <v>106.710644</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Quận 5 #35</t>
+          <t>Siêu thị Ân Nam - CN Bình Thạnh #35</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2267,7 +2268,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2279,18 +2280,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>98 Phan Đăng Lưu, Phường 3, Bình Thạnh, TP.HCM</t>
+          <t>98 Lê Thánh Tôn, P. Bến Nghé, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10.799485</v>
+        <v>10.776194</v>
       </c>
       <c r="D37" t="n">
-        <v>106.695172</v>
+        <v>106.704789</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Bình Thạnh #36</t>
+          <t>Phúc Long Hub - CN Quận 1 #36</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2318,7 +2319,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 1</t>
         </is>
       </c>
     </row>
@@ -2330,18 +2331,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>111 Quang Trung, Phường 10, Gò Vấp, TP.HCM</t>
+          <t>111 Ngô Gia Tự, Phường 4, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10.828865</v>
+        <v>10.762746</v>
       </c>
       <c r="D38" t="n">
-        <v>106.665837</v>
+        <v>106.672575</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Gò Vấp #37</t>
+          <t>WinMart+ - CN Quận 10 #37</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2369,7 +2370,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Gò Vấp; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2381,18 +2382,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>124 Nguyễn Trãi, Phường 11, Quận 5, TP.HCM</t>
+          <t>124 Lũy Bán Bích, P. Hòa Thạnh, Tân Phú, TP.HCM</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.756264</v>
+        <v>10.775725</v>
       </c>
       <c r="D39" t="n">
-        <v>106.659222</v>
+        <v>106.630129</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Circle K - CN Quận 5 #38</t>
+          <t>Circle K - CN Tân Phú #38</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2420,7 +2421,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Phú; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2432,18 +2433,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>137 Phan Xích Long, Phường 2, Phú Nhuận, TP.HCM</t>
+          <t>137 Nguyễn Thị Thập, P. Tân Phong, Quận 7, TP.HCM</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10.801849</v>
+        <v>10.74144</v>
       </c>
       <c r="D40" t="n">
-        <v>106.685896</v>
+        <v>106.708939</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Phú Nhuận #39</t>
+          <t>Highlands Coffee - CN Quận 7 #39</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2471,7 +2472,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2483,18 +2484,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>150 Nguyễn Huệ, P. Bến Nghé, Quận 1, TP.HCM</t>
+          <t>150 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10.774706</v>
+        <v>10.788862</v>
       </c>
       <c r="D41" t="n">
-        <v>106.700713</v>
+        <v>106.684005</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 1 #40</t>
+          <t>Bách Hóa Xanh - CN Quận 3 #40</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2522,7 +2523,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2534,18 +2535,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>163 Nguyễn Thị Thập, P. Tân Phú, Quận 7, TP.HCM</t>
+          <t>163 Hồng Bàng, Phường 11, Quận 5, TP.HCM</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10.735406</v>
+        <v>10.753383</v>
       </c>
       <c r="D42" t="n">
-        <v>106.715644</v>
+        <v>106.661158</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GS25 - CN Quận 7 #41</t>
+          <t>GS25 - CN Quận 5 #41</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2573,7 +2574,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2585,18 +2586,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>176 Nguyễn Văn Trỗi, Phường 8, Phú Nhuận, TP.HCM</t>
+          <t>176 Phan Văn Trị, Phường 7, Gò Vấp, TP.HCM</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.792078</v>
+        <v>10.822011</v>
       </c>
       <c r="D43" t="n">
-        <v>106.671171</v>
+        <v>106.687408</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Phú Nhuận #42</t>
+          <t>Nhà hàng Golden Gate - CN Gò Vấp #42</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2624,7 +2625,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Gò Vấp</t>
         </is>
       </c>
     </row>
@@ -2636,18 +2637,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>189 Lê Lợi, P. Bến Thành, Quận 1, TP.HCM</t>
+          <t>189 Kha Vạn Cân, P. Linh Đông, TP. Thủ Đức, TP.HCM</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10.776318</v>
+        <v>10.840187</v>
       </c>
       <c r="D44" t="n">
-        <v>106.6981</v>
+        <v>106.74242</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Quận 1 #43</t>
+          <t>Đại lý Phân Phối Minh Phát - CN TP. Thủ Đức #43</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2675,7 +2676,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2687,18 +2688,18 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>202 Nguyễn Văn Linh, P. Tân Phong, Quận 7, TP.HCM</t>
+          <t>202 Sư Vạn Hạnh, Phường 13, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10.728547</v>
+        <v>10.775819</v>
       </c>
       <c r="D45" t="n">
-        <v>106.705444</v>
+        <v>106.665458</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Co.op Food - CN Quận 7 #44</t>
+          <t>Co.op Food - CN Quận 10 #44</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2726,7 +2727,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2738,14 +2739,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>215 Cộng Hòa, Phường 13, Tân Bình, TP.HCM</t>
+          <t>215 Lý Thường Kiệt, Phường 8, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10.80102</v>
+        <v>10.786068</v>
       </c>
       <c r="D46" t="n">
-        <v>106.647635</v>
+        <v>106.653974</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2789,18 +2790,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>228 Hai Bà Trưng, P. Tân Định, Quận 1, TP.HCM</t>
+          <t>228 Lê Quang Định, Phường 14, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10.790299</v>
+        <v>10.81164</v>
       </c>
       <c r="D47" t="n">
-        <v>106.695039</v>
+        <v>106.696656</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Quận 1 #46</t>
+          <t>Phúc Long Hub - CN Bình Thạnh #46</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2828,7 +2829,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2840,18 +2841,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>241 Sư Vạn Hạnh, Phường 12, Quận 10, TP.HCM</t>
+          <t>241 Cô Giang, P. Cô Giang, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10.769313</v>
+        <v>10.763445</v>
       </c>
       <c r="D48" t="n">
-        <v>106.669366</v>
+        <v>106.694426</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Quận 10 #47</t>
+          <t>WinMart+ - CN Quận 1 #47</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2879,7 +2880,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2891,18 +2892,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>254 Trường Chinh, Phường 15, Tân Bình, TP.HCM</t>
+          <t>254 Nguyễn Trãi, Phường 8, Quận 5, TP.HCM</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10.816112</v>
+        <v>10.754845</v>
       </c>
       <c r="D49" t="n">
-        <v>106.628374</v>
+        <v>106.67113</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Circle K - CN Tân Bình #48</t>
+          <t>Circle K - CN Quận 5 #48</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2930,7 +2931,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 5</t>
         </is>
       </c>
     </row>
@@ -2942,18 +2943,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>267 Võ Văn Tần, Phường 6, Quận 3, TP.HCM</t>
+          <t>267 Phan Đăng Lưu, Phường 3, Phú Nhuận, TP.HCM</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10.77883</v>
+        <v>10.801472</v>
       </c>
       <c r="D50" t="n">
-        <v>106.685933</v>
+        <v>106.681373</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Quận 3 #49</t>
+          <t>Highlands Coffee - CN Phú Nhuận #49</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2981,7 +2982,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -2993,18 +2994,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>280 Ba Tháng Hai, Phường 11, Quận 10, TP.HCM</t>
+          <t>280 Song Hành Xa Lộ Hà Nội, P. Thảo Điền, TP. Thủ Đức, TP.HCM</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10.7736</v>
+        <v>10.80474</v>
       </c>
       <c r="D51" t="n">
-        <v>106.676441</v>
+        <v>106.739496</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 10 #50</t>
+          <t>Bách Hóa Xanh - CN TP. Thủ Đức #50</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3032,7 +3033,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3044,18 +3045,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>293 Võ Văn Ngân, P. Linh Chiểu, TP. Thủ Đức, TP.HCM</t>
+          <t>293 Nguyễn Đình Chiểu, Phường 5, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10.850265</v>
+        <v>10.771706</v>
       </c>
       <c r="D52" t="n">
-        <v>106.762668</v>
+        <v>106.683887</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GS25 - CN TP. Thủ Đức #51</t>
+          <t>GS25 - CN Quận 3 #51</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3083,7 +3084,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3095,18 +3096,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>306 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3, TP.HCM</t>
+          <t>306 Bình Tiên, Phường 3, Quận 6, TP.HCM</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10.790338</v>
+        <v>10.748215</v>
       </c>
       <c r="D53" t="n">
-        <v>106.685688</v>
+        <v>106.650515</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Quận 3 #52</t>
+          <t>Nhà hàng Golden Gate - CN Quận 6 #52</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3134,7 +3135,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 6; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3150,10 +3151,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10.798641</v>
+        <v>10.800176</v>
       </c>
       <c r="D54" t="n">
-        <v>106.712546</v>
+        <v>106.715018</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3197,18 +3198,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>332 Xa Lộ Hà Nội, P. An Phú, TP. Thủ Đức, TP.HCM</t>
+          <t>332 Lê Lợi, P. Bến Thành, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10.797518</v>
+        <v>10.771407</v>
       </c>
       <c r="D55" t="n">
-        <v>106.745598</v>
+        <v>106.698919</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Co.op Food - CN TP. Thủ Đức #54</t>
+          <t>Co.op Food - CN Quận 1 #54</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3236,7 +3237,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 1</t>
         </is>
       </c>
     </row>
@@ -3248,18 +3249,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>345 Trần Hưng Đạo, Phường 7, Quận 5, TP.HCM</t>
+          <t>345 Lý Thường Kiệt, Phường 14, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10.754865</v>
+        <v>10.772826</v>
       </c>
       <c r="D56" t="n">
-        <v>106.676115</v>
+        <v>106.659246</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Quận 5 #55</t>
+          <t>Siêu thị Ân Nam - CN Quận 10 #55</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3287,7 +3288,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3299,18 +3300,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>358 Phan Đăng Lưu, Phường 3, Bình Thạnh, TP.HCM</t>
+          <t>358 Tân Kỳ Tân Quý, P. Sơn Kỳ, Tân Phú, TP.HCM</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10.8034</v>
+        <v>10.80146</v>
       </c>
       <c r="D57" t="n">
-        <v>106.693464</v>
+        <v>106.624705</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Bình Thạnh #56</t>
+          <t>Phúc Long Hub - CN Tân Phú #56</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3338,7 +3339,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Phú; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3350,18 +3351,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>371 Quang Trung, Phường 10, Gò Vấp, TP.HCM</t>
+          <t>371 Nguyễn Hữu Thọ, P. Tân Hưng, Quận 7, TP.HCM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10.833203</v>
+        <v>10.746081</v>
       </c>
       <c r="D58" t="n">
-        <v>106.658408</v>
+        <v>106.700003</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Gò Vấp #57</t>
+          <t>WinMart+ - CN Quận 7 #57</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3389,7 +3390,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Gò Vấp; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3401,18 +3402,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>384 Nguyễn Trãi, Phường 11, Quận 5, TP.HCM</t>
+          <t>384 Cách Mạng Tháng 8, Phường 10, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10.750186</v>
+        <v>10.780294</v>
       </c>
       <c r="D59" t="n">
-        <v>106.663989</v>
+        <v>106.675036</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Circle K - CN Quận 5 #58</t>
+          <t>Circle K - CN Quận 3 #58</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3440,7 +3441,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3452,18 +3453,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17 Phan Xích Long, Phường 2, Phú Nhuận, TP.HCM</t>
+          <t>17 Hải Thượng Lãn Ông, Phường 10, Quận 5, TP.HCM</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10.795946</v>
+        <v>10.749378</v>
       </c>
       <c r="D60" t="n">
-        <v>106.685455</v>
+        <v>106.660462</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Phú Nhuận #59</t>
+          <t>Highlands Coffee - CN Quận 5 #59</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3491,7 +3492,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3503,18 +3504,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30 Nguyễn Huệ, P. Bến Nghé, Quận 1, TP.HCM</t>
+          <t>30 Quang Trung, Phường 10, Gò Vấp, TP.HCM</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10.771178</v>
+        <v>10.827451</v>
       </c>
       <c r="D61" t="n">
-        <v>106.701789</v>
+        <v>106.670435</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 1 #60</t>
+          <t>Bách Hóa Xanh - CN Gò Vấp #60</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3542,7 +3543,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Gò Vấp</t>
         </is>
       </c>
     </row>
@@ -3554,18 +3555,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>43 Nguyễn Thị Thập, P. Tân Phú, Quận 7, TP.HCM</t>
+          <t>43 Nguyễn Thị Minh Khai, P. Đa Kao, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10.738455</v>
+        <v>10.787302</v>
       </c>
       <c r="D62" t="n">
-        <v>106.713817</v>
+        <v>106.700127</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GS25 - CN Quận 7 #61</t>
+          <t>GS25 - CN Quận 1 #61</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3593,7 +3594,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3605,18 +3606,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>56 Nguyễn Văn Trỗi, Phường 8, Phú Nhuận, TP.HCM</t>
+          <t>56 Tô Hiến Thành, Phường 15, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10.798059</v>
+        <v>10.781104</v>
       </c>
       <c r="D63" t="n">
-        <v>106.67215</v>
+        <v>106.6628</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Phú Nhuận #62</t>
+          <t>Nhà hàng Golden Gate - CN Quận 10 #62</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3644,7 +3645,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3656,18 +3657,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>69 Lê Lợi, P. Bến Thành, Quận 1, TP.HCM</t>
+          <t>69 Lạc Long Quân, Phường 10, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10.771266</v>
+        <v>10.780166</v>
       </c>
       <c r="D64" t="n">
-        <v>106.70061</v>
+        <v>106.646724</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Quận 1 #63</t>
+          <t>Đại lý Phân Phối Minh Phát - CN Tân Bình #63</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3695,7 +3696,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3707,18 +3708,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>82 Nguyễn Văn Linh, P. Tân Phong, Quận 7, TP.HCM</t>
+          <t>82 Nguyễn Hữu Cảnh, Phường 22, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10.732453</v>
+        <v>10.793981</v>
       </c>
       <c r="D65" t="n">
-        <v>106.713121</v>
+        <v>106.720528</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Co.op Food - CN Quận 7 #64</t>
+          <t>Co.op Food - CN Bình Thạnh #64</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3746,7 +3747,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3758,18 +3759,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>95 Cộng Hòa, Phường 13, Tân Bình, TP.HCM</t>
+          <t>95 Đinh Tiên Hoàng, P. Đa Kao, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10.804935</v>
+        <v>10.790934</v>
       </c>
       <c r="D66" t="n">
-        <v>106.650121</v>
+        <v>106.698968</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Tân Bình #65</t>
+          <t>Siêu thị Ân Nam - CN Quận 1 #65</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3797,7 +3798,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3809,18 +3810,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>108 Hai Bà Trưng, P. Tân Định, Quận 1, TP.HCM</t>
+          <t>108 Trần Hưng Đạo, Phường 2, Quận 5, TP.HCM</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10.78936</v>
+        <v>10.756264</v>
       </c>
       <c r="D67" t="n">
-        <v>106.690117</v>
+        <v>106.679987</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Quận 1 #66</t>
+          <t>Phúc Long Hub - CN Quận 5 #66</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3848,7 +3849,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 5</t>
         </is>
       </c>
     </row>
@@ -3860,18 +3861,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>121 Sư Vạn Hạnh, Phường 12, Quận 10, TP.HCM</t>
+          <t>121 Nguyễn Văn Trỗi, Phường 11, Phú Nhuận, TP.HCM</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10.773526</v>
+        <v>10.795131</v>
       </c>
       <c r="D68" t="n">
-        <v>106.666865</v>
+        <v>106.673426</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Quận 10 #67</t>
+          <t>WinMart+ - CN Phú Nhuận #67</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3899,7 +3900,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3911,18 +3912,18 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>134 Trường Chinh, Phường 15, Tân Bình, TP.HCM</t>
+          <t>134 Trần Não, P. An Khánh, TP. Thủ Đức, TP.HCM</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10.818224</v>
+        <v>10.788389</v>
       </c>
       <c r="D69" t="n">
-        <v>106.62902</v>
+        <v>106.730388</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Circle K - CN Tân Bình #68</t>
+          <t>Circle K - CN TP. Thủ Đức #68</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3950,7 +3951,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -3962,14 +3963,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>147 Võ Văn Tần, Phường 6, Quận 3, TP.HCM</t>
+          <t>147 Kỳ Đồng, Phường 9, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10.774024</v>
+        <v>10.78225</v>
       </c>
       <c r="D70" t="n">
-        <v>106.686908</v>
+        <v>106.679763</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4013,18 +4014,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>160 Ba Tháng Hai, Phường 11, Quận 10, TP.HCM</t>
+          <t>160 Cộng Hòa, Phường 13, Tân Bình, TP.HCM</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10.770281</v>
+        <v>10.801112</v>
       </c>
       <c r="D71" t="n">
-        <v>106.677601</v>
+        <v>106.64326</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 10 #70</t>
+          <t>Bách Hóa Xanh - CN Tân Bình #70</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4052,7 +4053,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Bình; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4064,18 +4065,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>173 Võ Văn Ngân, P. Linh Chiểu, TP. Thủ Đức, TP.HCM</t>
+          <t>173 Bạch Đằng, Phường 15, Bình Thạnh, TP.HCM</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10.846985</v>
+        <v>10.801394</v>
       </c>
       <c r="D72" t="n">
-        <v>106.766131</v>
+        <v>106.702572</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GS25 - CN TP. Thủ Đức #71</t>
+          <t>GS25 - CN Bình Thạnh #71</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4103,7 +4104,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4115,18 +4116,18 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>186 Nam Kỳ Khởi Nghĩa, Phường 8, Quận 3, TP.HCM</t>
+          <t>186 Nguyễn Trãi, P. Nguyễn Cư Trinh, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.790243</v>
+        <v>10.767577</v>
       </c>
       <c r="D73" t="n">
-        <v>106.683199</v>
+        <v>106.68722</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nhà hàng Golden Gate - CN Quận 3 #72</t>
+          <t>Nhà hàng Golden Gate - CN Quận 1 #72</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4154,7 +4155,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Quận 1</t>
         </is>
       </c>
     </row>
@@ -4166,18 +4167,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>199 Điện Biên Phủ, Phường 25, Bình Thạnh, TP.HCM</t>
+          <t>199 Nguyễn Tri Phương, Phường 8, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10.79837</v>
+        <v>10.760668</v>
       </c>
       <c r="D74" t="n">
-        <v>106.714523</v>
+        <v>106.667509</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Đại lý Phân Phối Minh Phát - CN Bình Thạnh #73</t>
+          <t>Đại lý Phân Phối Minh Phát - CN Quận 10 #73</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4205,7 +4206,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4217,18 +4218,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>212 Xa Lộ Hà Nội, P. An Phú, TP. Thủ Đức, TP.HCM</t>
+          <t>212 Hòa Bình, P. Hiệp Tân, Tân Phú, TP.HCM</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10.796051</v>
+        <v>10.76672</v>
       </c>
       <c r="D75" t="n">
-        <v>106.739911</v>
+        <v>106.631945</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Co.op Food - CN TP. Thủ Đức #74</t>
+          <t>Co.op Food - CN Tân Phú #74</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4256,7 +4257,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Kênh GT/MT TP. Thủ Đức; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Tân Phú; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4268,18 +4269,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>225 Trần Hưng Đạo, Phường 7, Quận 5, TP.HCM</t>
+          <t>225 Huỳnh Tấn Phát, P. Bình Thuận, Quận 7, TP.HCM</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10.757987</v>
+        <v>10.743075</v>
       </c>
       <c r="D76" t="n">
-        <v>106.674345</v>
+        <v>106.726938</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Siêu thị Ân Nam - CN Quận 5 #75</t>
+          <t>Siêu thị Ân Nam - CN Quận 7 #75</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4307,7 +4308,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 7; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4319,18 +4320,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>238 Phan Đăng Lưu, Phường 3, Bình Thạnh, TP.HCM</t>
+          <t>238 Điện Biên Phủ, Phường 4, Quận 3, TP.HCM</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10.799852</v>
+        <v>10.773041</v>
       </c>
       <c r="D77" t="n">
-        <v>106.686701</v>
+        <v>106.6794</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Phúc Long Hub - CN Bình Thạnh #76</t>
+          <t>Phúc Long Hub - CN Quận 3 #76</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4358,7 +4359,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Bình Thạnh; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 3; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4370,18 +4371,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>251 Quang Trung, Phường 10, Gò Vấp, TP.HCM</t>
+          <t>251 Hậu Giang, Phường 6, Quận 6, TP.HCM</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10.832621</v>
+        <v>10.749548</v>
       </c>
       <c r="D78" t="n">
-        <v>106.660475</v>
+        <v>106.64573</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>WinMart+ - CN Gò Vấp #77</t>
+          <t>WinMart+ - CN Quận 6 #77</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4409,7 +4410,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Gò Vấp; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 6; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4421,18 +4422,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>264 Nguyễn Trãi, Phường 11, Quận 5, TP.HCM</t>
+          <t>264 Nguyễn Oanh, Phường 17, Gò Vấp, TP.HCM</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10.755421</v>
+        <v>10.836088</v>
       </c>
       <c r="D79" t="n">
-        <v>106.659648</v>
+        <v>106.675299</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Circle K - CN Quận 5 #78</t>
+          <t>Circle K - CN Gò Vấp #78</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4460,7 +4461,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 5; giao kiện tiêu chuẩn</t>
+          <t>BACKHAUL_PICKUP: Thu hồi kiện hàng/bao bì chiều về kho từ Gò Vấp</t>
         </is>
       </c>
     </row>
@@ -4472,18 +4473,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>277 Phan Xích Long, Phường 2, Phú Nhuận, TP.HCM</t>
+          <t>277 Hai Bà Trưng, P. Tân Định, Quận 1, TP.HCM</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10.796284</v>
+        <v>10.789214</v>
       </c>
       <c r="D80" t="n">
-        <v>106.689112</v>
+        <v>106.692925</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Highlands Coffee - CN Phú Nhuận #79</t>
+          <t>Highlands Coffee - CN Quận 1 #79</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4511,7 +4512,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Phú Nhuận; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
         </is>
       </c>
     </row>
@@ -4523,18 +4524,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>290 Nguyễn Huệ, P. Bến Nghé, Quận 1, TP.HCM</t>
+          <t>290 Thành Thái, Phường 14, Quận 10, TP.HCM</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10.771287</v>
+        <v>10.772795</v>
       </c>
       <c r="D81" t="n">
-        <v>106.702477</v>
+        <v>106.660711</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bách Hóa Xanh - CN Quận 1 #80</t>
+          <t>Bách Hóa Xanh - CN Quận 10 #80</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4562,7 +4563,333 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Kênh GT/MT Quận 1; giao kiện tiêu chuẩn</t>
+          <t>Kênh GT/MT Quận 10; giao kiện tiêu chuẩn</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>plate</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>capacity_kg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>l_per_100km</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>51C-000.01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>van_500</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>51C-000.02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>truck_800</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>51C-000.03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>truck_1000</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>51C-000.04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>truck_1500</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>51C-000.05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>truck_2000</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>51C-000.06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>van_500</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>51C-000.07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>truck_800</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>800</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>51C-000.08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>truck_1000</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>51C-000.09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>truck_1500</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>51C-000.10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>truck_2000</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ready</t>
         </is>
       </c>
     </row>
